--- a/WorkBot/refactor-experimental/data/orders/Hill & Markes/Hill & Markes_Triphammer_20251114.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/Hill & Markes/Hill & Markes_Triphammer_20251114.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,20 +454,14 @@
           <t>Cup - Hot (12oz)</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>62.78</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>125.56</t>
-        </is>
+      <c r="C2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" t="n">
+        <v>62.78</v>
+      </c>
+      <c r="E2" t="n">
+        <v>125.56</v>
       </c>
     </row>
     <row r="3">
@@ -481,20 +475,14 @@
           <t>Cup - Hot (16oz)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>70.09</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>140.18</t>
-        </is>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="n">
+        <v>70.09</v>
+      </c>
+      <c r="E3" t="n">
+        <v>140.18</v>
       </c>
     </row>
     <row r="4">
@@ -508,20 +496,14 @@
           <t>Cup - Hot (20oz)</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>83.13</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>83.13</t>
-        </is>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>83.13</v>
+      </c>
+      <c r="E4" t="n">
+        <v>83.13</v>
       </c>
     </row>
     <row r="5">
@@ -535,20 +517,14 @@
           <t>Lid Cold Dome 16/24oz</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>66.62</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>66.62</t>
-        </is>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>66.62</v>
+      </c>
+      <c r="E5" t="n">
+        <v>66.62</v>
       </c>
     </row>
     <row r="6">
@@ -562,20 +538,14 @@
           <t>Trash Bag (33x40)</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>25.30</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>25.30</t>
-        </is>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="E6" t="n">
+        <v>25.3</v>
       </c>
     </row>
     <row r="7">
@@ -589,20 +559,35 @@
           <t>Lid Serving Bowl - 160oz (square)</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>29.67</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>29.67</t>
-        </is>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>29.67</v>
+      </c>
+      <c r="E7" t="n">
+        <v>29.67</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>P4040XC</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Bag Sheet Pan Cover 30x43</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" t="n">
+        <v>31.89</v>
+      </c>
+      <c r="E8" t="n">
+        <v>63.78</v>
       </c>
     </row>
   </sheetData>

--- a/WorkBot/refactor-experimental/data/orders/Hill & Markes/Hill & Markes_Triphammer_20251114.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/Hill & Markes/Hill & Markes_Triphammer_20251114.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -590,6 +590,237 @@
         <v>63.78</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>SAB12032T300</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Cont Salad - 32oz Sabert (Round)</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" t="n">
+        <v>95.09999999999999</v>
+      </c>
+      <c r="E9" t="n">
+        <v>285.3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>TS12</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Tamper Evident - 12oz Square</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>38.39</v>
+      </c>
+      <c r="E10" t="n">
+        <v>38.39</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>TS16</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Tamper Evident - 16oz</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>41.88</v>
+      </c>
+      <c r="E11" t="n">
+        <v>41.88</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>TS8</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Tamper Evident - 8oz</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>38.29</v>
+      </c>
+      <c r="E12" t="n">
+        <v>38.29</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>K250</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Towel Paper Roll (White)</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" t="n">
+        <v>33.15</v>
+      </c>
+      <c r="E13" t="n">
+        <v>66.3</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>HIMF1824XC</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Bag - Poly (10x8x24, 1.25mil)</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="n">
+        <v>69.48999999999999</v>
+      </c>
+      <c r="E14" t="n">
+        <v>69.48999999999999</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>4541602</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Container - Anchor (16oz)</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="n">
+        <v>43.72</v>
+      </c>
+      <c r="E15" t="n">
+        <v>43.72</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ANPM424</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Container - Anchor (24oz)</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" t="n">
+        <v>47.17</v>
+      </c>
+      <c r="E16" t="n">
+        <v>47.17</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ANPLC4LD</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Lid Anchor - 24/32oz (Dome)</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="n">
+        <v>56.82</v>
+      </c>
+      <c r="E17" t="n">
+        <v>56.82</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ANPLC4F</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Lid Anchor - 24/32oz (Flat)</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" t="n">
+        <v>66.89</v>
+      </c>
+      <c r="E18" t="n">
+        <v>66.89</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>SAB52032T300</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Lid Salad - 24/32oz Sabert (Round)</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>3</v>
+      </c>
+      <c r="D19" t="n">
+        <v>87.28</v>
+      </c>
+      <c r="E19" t="n">
+        <v>261.84</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
